--- a/LULU.xlsx
+++ b/LULU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE990D7-0AD9-4D23-BFD0-0E4B2735B275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{151AACC3-BE01-4E96-99F1-689FE34CCC92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2340" windowWidth="38175" windowHeight="15240" xr2:uid="{307BA413-EEF9-4958-8DCC-E913E47A6543}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{307BA413-EEF9-4958-8DCC-E913E47A6543}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="303">
   <si>
     <t>SEC</t>
   </si>
@@ -964,9 +964,6 @@
     <t>Founded:</t>
   </si>
   <si>
-    <t>(pior at Nike Consumer, Product &amp; Brand)</t>
-  </si>
-  <si>
     <t>Meghan Frank</t>
   </si>
   <si>
@@ -989,6 +986,27 @@
   </si>
   <si>
     <t>management publicly</t>
+  </si>
+  <si>
+    <t>Q226:</t>
+  </si>
+  <si>
+    <t>Weak leggins -&gt; down 20%</t>
+  </si>
+  <si>
+    <t>(pior at Nike Consumer, Product &amp; Brand, joins 09.09)</t>
+  </si>
+  <si>
+    <t>Outlook</t>
+  </si>
+  <si>
+    <t>China weakens, brand problems rather than macro</t>
+  </si>
+  <si>
+    <t>For full year: Revenue down 5-7% (10.35-10,5)</t>
+  </si>
+  <si>
+    <t>EPS: 9,48-9,73</t>
   </si>
 </sst>
 </file>
@@ -1006,13 +1024,19 @@
     <numFmt numFmtId="171" formatCode="0.0%"/>
     <numFmt numFmtId="172" formatCode="&quot;FY&quot;0&quot;A&quot;"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1369,176 +1393,180 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="4" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="171" fontId="4" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="15" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="171" fontId="4" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="13" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="13" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="22" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="13" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="13" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="13" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="13" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="23" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="15" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="15" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="171" fontId="3" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="171" fontId="3" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="12" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="12" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="21" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="12" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="12" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="12" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="12" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="22" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="14" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1597,16 +1625,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>42863</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>9526</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>71438</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>38101</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1621,8 +1649,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9844088" y="171450"/>
-          <a:ext cx="28575" cy="5210175"/>
+          <a:off x="10420351" y="285750"/>
+          <a:ext cx="28575" cy="7315200"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2097,7 +2125,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0763D264-7AA2-4A43-9561-8F9D88497622}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="2" customWidth="1"/>
@@ -2119,7 +2147,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="16">
-        <v>110.86</v>
+        <v>99.65</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -2127,10 +2155,10 @@
         <v>27</v>
       </c>
       <c r="I3" s="3">
-        <v>108.437957</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>120</v>
+        <v>105.594064</v>
+      </c>
+      <c r="J3" s="100" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -2150,7 +2178,7 @@
       </c>
       <c r="I4" s="7">
         <f>I3*I2</f>
-        <v>12021.43191302</v>
+        <v>10522.448477600001</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -2169,10 +2197,10 @@
         <v>4</v>
       </c>
       <c r="I5" s="7">
-        <v>1514.729</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>120</v>
+        <v>189.73699999999999</v>
+      </c>
+      <c r="J5" s="100" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -2182,8 +2210,8 @@
       <c r="I6" s="7">
         <v>0</v>
       </c>
-      <c r="J6" s="18" t="s">
-        <v>120</v>
+      <c r="J6" s="100" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -2195,7 +2223,7 @@
       </c>
       <c r="I7" s="7">
         <f>I4+I6-I5</f>
-        <v>10506.702913020001</v>
+        <v>10332.711477600002</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -2217,8 +2245,8 @@
         <v>62</v>
       </c>
       <c r="I9" s="8">
-        <f>+I4/Model!Z36</f>
-        <v>6.6247800708359215</v>
+        <f>+I2/9.73</f>
+        <v>10.241521068859198</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -2227,12 +2255,12 @@
       </c>
       <c r="I10" s="8">
         <f>+I7/Model!Z32</f>
-        <v>4.193125869975499</v>
+        <v>4.1236875318923234</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B12" s="49" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H12" s="86" t="s">
         <v>284</v>
@@ -2240,29 +2268,29 @@
       <c r="I12" s="86" t="s">
         <v>285</v>
       </c>
-      <c r="K12" s="86" t="s">
-        <v>288</v>
+      <c r="K12" s="101" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B13" s="86" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H13" s="86" t="s">
         <v>286</v>
       </c>
       <c r="I13" s="86" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B14" s="86" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B15" s="86" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H15" s="86" t="s">
         <v>287</v>
@@ -2271,17 +2299,47 @@
         <v>1998</v>
       </c>
       <c r="J15" s="86" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B16" s="86" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" s="86" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B19" s="101" t="s">
         <v>296</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B20" s="101" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B21" s="101" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B22" s="26" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B23" s="101" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B24" s="101" t="s">
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -2290,6 +2348,7 @@
     <hyperlink ref="B5" r:id="rId2" xr:uid="{C8DE1C41-8830-452C-99CA-03BBB7F2E4E3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -2852,7 +2911,9 @@
       <c r="O11" s="4">
         <v>476</v>
       </c>
-      <c r="P11" s="4"/>
+      <c r="P11" s="4">
+        <v>483</v>
+      </c>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
       <c r="T11" s="4">
@@ -2927,7 +2988,9 @@
       <c r="O12" s="4">
         <v>173</v>
       </c>
-      <c r="P12" s="4"/>
+      <c r="P12" s="4">
+        <v>174</v>
+      </c>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
       <c r="T12" s="4">
@@ -2998,7 +3061,9 @@
       <c r="O13" s="4">
         <v>117</v>
       </c>
-      <c r="P13" s="4"/>
+      <c r="P13" s="4">
+        <v>117</v>
+      </c>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
       <c r="T13" s="4">
@@ -3073,7 +3138,9 @@
       <c r="O14" s="4">
         <v>50</v>
       </c>
-      <c r="P14" s="4"/>
+      <c r="P14" s="4">
+        <v>51</v>
+      </c>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
       <c r="T14" s="4">
@@ -3138,7 +3205,7 @@
         <v>749</v>
       </c>
       <c r="J15" s="9">
-        <f t="shared" ref="J15:O15" si="5">+SUM(J11:J14)</f>
+        <f t="shared" ref="J15:P15" si="5">+SUM(J11:J14)</f>
         <v>767</v>
       </c>
       <c r="K15" s="9">
@@ -3161,7 +3228,10 @@
         <f t="shared" si="5"/>
         <v>816</v>
       </c>
-      <c r="P15" s="9"/>
+      <c r="P15" s="9">
+        <f t="shared" si="5"/>
+        <v>825</v>
+      </c>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
       <c r="S15" s="1"/>
@@ -3282,7 +3352,10 @@
         <f>+O24/O15</f>
         <v>1.4618137254901959</v>
       </c>
-      <c r="P16" s="10"/>
+      <c r="P16" s="10">
+        <f>+P24/P15</f>
+        <v>1.4227236363636364</v>
+      </c>
       <c r="Q16" s="10"/>
       <c r="R16" s="10"/>
       <c r="T16" s="10">
@@ -3417,7 +3490,9 @@
       <c r="O18" s="3">
         <v>1621.21</v>
       </c>
-      <c r="P18" s="3"/>
+      <c r="P18" s="3">
+        <v>1616.7719999999999</v>
+      </c>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
@@ -3522,7 +3597,9 @@
       <c r="O19" s="3">
         <v>529.803</v>
       </c>
-      <c r="P19" s="3"/>
+      <c r="P19" s="3">
+        <v>458.51400000000001</v>
+      </c>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
@@ -3623,7 +3700,9 @@
       <c r="O20" s="3">
         <v>320.58999999999997</v>
       </c>
-      <c r="P20" s="3"/>
+      <c r="P20" s="3">
+        <v>340.34500000000003</v>
+      </c>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
@@ -3724,7 +3803,9 @@
       <c r="O21" s="3">
         <v>1602.9849999999999</v>
       </c>
-      <c r="P21" s="3"/>
+      <c r="P21" s="3">
+        <v>1488.241</v>
+      </c>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
@@ -3825,7 +3906,9 @@
       <c r="O22" s="3">
         <v>581.87800000000004</v>
       </c>
-      <c r="P22" s="3"/>
+      <c r="P22" s="3">
+        <v>621.38</v>
+      </c>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
@@ -3926,7 +4009,9 @@
       <c r="O23" s="3">
         <v>286.74</v>
       </c>
-      <c r="P23" s="3"/>
+      <c r="P23" s="3">
+        <v>306.01</v>
+      </c>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
@@ -4027,7 +4112,9 @@
       <c r="O24" s="3">
         <v>1192.8399999999999</v>
       </c>
-      <c r="P24" s="3"/>
+      <c r="P24" s="3">
+        <v>1173.7470000000001</v>
+      </c>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
@@ -4149,7 +4236,9 @@
       <c r="O25" s="3">
         <v>997.44200000000001</v>
       </c>
-      <c r="P25" s="3"/>
+      <c r="P25" s="3">
+        <v>934.63</v>
+      </c>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
@@ -4271,7 +4360,9 @@
       <c r="O26" s="3">
         <v>281.32100000000003</v>
       </c>
-      <c r="P26" s="3"/>
+      <c r="P26" s="3">
+        <v>307.25400000000002</v>
+      </c>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
@@ -4391,7 +4482,9 @@
       <c r="O27" s="11">
         <v>2471.6030000000001</v>
       </c>
-      <c r="P27" s="11"/>
+      <c r="P27" s="11">
+        <v>2415.6309999999999</v>
+      </c>
       <c r="Q27" s="11"/>
       <c r="R27" s="11"/>
       <c r="S27" s="3"/>
@@ -4492,7 +4585,9 @@
       <c r="O28" s="3">
         <v>1132.7850000000001</v>
       </c>
-      <c r="P28" s="3"/>
+      <c r="P28" s="3">
+        <v>953.75300000000004</v>
+      </c>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
@@ -4546,7 +4641,7 @@
         <v>1275.0680000000002</v>
       </c>
       <c r="H29" s="3">
-        <f t="shared" ref="H29:O29" si="26">H27-H28</f>
+        <f t="shared" ref="H29:P29" si="26">H27-H28</f>
         <v>1412.1849999999999</v>
       </c>
       <c r="I29" s="3">
@@ -4577,7 +4672,10 @@
         <f t="shared" si="26"/>
         <v>1338.818</v>
       </c>
-      <c r="P29" s="3"/>
+      <c r="P29" s="3">
+        <f t="shared" si="26"/>
+        <v>1461.8779999999997</v>
+      </c>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
@@ -4658,7 +4756,9 @@
       <c r="O30" s="3">
         <v>1059.9880000000001</v>
       </c>
-      <c r="P30" s="3"/>
+      <c r="P30" s="3">
+        <v>1006.332</v>
+      </c>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
@@ -4732,7 +4832,9 @@
       <c r="O31" s="3">
         <v>1.8839999999999999</v>
       </c>
-      <c r="P31" s="3"/>
+      <c r="P31" s="3">
+        <v>1.893</v>
+      </c>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
@@ -4790,7 +4892,7 @@
         <v>432.64200000000017</v>
       </c>
       <c r="H32" s="3">
-        <f t="shared" ref="H32:O32" si="35">H29-SUM(H30:H31)</f>
+        <f t="shared" ref="H32:P32" si="35">H29-SUM(H30:H31)</f>
         <v>540.226</v>
       </c>
       <c r="I32" s="3">
@@ -4821,7 +4923,10 @@
         <f t="shared" si="35"/>
         <v>276.94599999999991</v>
       </c>
-      <c r="P32" s="3"/>
+      <c r="P32" s="3">
+        <f t="shared" si="35"/>
+        <v>453.65299999999968</v>
+      </c>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
@@ -4914,7 +5019,9 @@
       <c r="O33" s="3">
         <v>9.1310000000000002</v>
       </c>
-      <c r="P33" s="3"/>
+      <c r="P33" s="3">
+        <v>13.698</v>
+      </c>
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
@@ -4968,7 +5075,7 @@
         <v>455.92500000000018</v>
       </c>
       <c r="H34" s="3">
-        <f t="shared" ref="H34:O34" si="43">H32+H33</f>
+        <f t="shared" ref="H34:P34" si="43">H32+H33</f>
         <v>558.22</v>
       </c>
       <c r="I34" s="3">
@@ -4999,7 +5106,10 @@
         <f t="shared" si="43"/>
         <v>286.07699999999988</v>
       </c>
-      <c r="P34" s="3"/>
+      <c r="P34" s="3">
+        <f t="shared" si="43"/>
+        <v>467.35099999999966</v>
+      </c>
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
@@ -5080,7 +5190,9 @@
       <c r="O35" s="3">
         <v>91.028999999999996</v>
       </c>
-      <c r="P35" s="3"/>
+      <c r="P35" s="3">
+        <v>138.12799999999999</v>
+      </c>
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
@@ -5134,7 +5246,7 @@
         <v>321.42100000000016</v>
       </c>
       <c r="H36" s="3">
-        <f t="shared" ref="H36:O36" si="52">H34-H35</f>
+        <f t="shared" ref="H36:P36" si="52">H34-H35</f>
         <v>392.92200000000003</v>
       </c>
       <c r="I36" s="3">
@@ -5165,7 +5277,10 @@
         <f t="shared" si="52"/>
         <v>195.04799999999989</v>
       </c>
-      <c r="P36" s="3"/>
+      <c r="P36" s="3">
+        <f t="shared" si="52"/>
+        <v>329.22299999999967</v>
+      </c>
       <c r="Q36" s="3"/>
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
@@ -5233,7 +5348,7 @@
         <v>28</v>
       </c>
       <c r="C38" s="14">
-        <f t="shared" ref="C38:O38" si="54">C36/C39</f>
+        <f t="shared" ref="C38:P38" si="54">C36/C39</f>
         <v>2.2822328403250376</v>
       </c>
       <c r="D38" s="14">
@@ -5284,7 +5399,10 @@
         <f t="shared" si="54"/>
         <v>1.689985616996204</v>
       </c>
-      <c r="P38" s="14"/>
+      <c r="P38" s="14">
+        <f t="shared" si="54"/>
+        <v>2.9161101170968458</v>
+      </c>
       <c r="Q38" s="14"/>
       <c r="R38" s="14"/>
       <c r="S38" s="14"/>
@@ -5372,7 +5490,9 @@
       <c r="O39" s="2">
         <v>115.414</v>
       </c>
-      <c r="P39" s="3"/>
+      <c r="P39" s="3">
+        <v>112.898</v>
+      </c>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
@@ -5550,7 +5670,10 @@
         <f>+O15/K15-1</f>
         <v>5.9740259740259649E-2</v>
       </c>
-      <c r="P43" s="3"/>
+      <c r="P43" s="13">
+        <f>+P15/L15-1</f>
+        <v>5.2295918367347038E-2</v>
+      </c>
       <c r="Q43" s="3"/>
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
@@ -5816,10 +5939,13 @@
         <v>8.1140867623592516E-3</v>
       </c>
       <c r="O46" s="12">
-        <f t="shared" ref="O46" si="66">O27/K27-1</f>
+        <f t="shared" ref="O46:P46" si="66">O27/K27-1</f>
         <v>4.258012536593192E-2</v>
       </c>
-      <c r="P46" s="13"/>
+      <c r="P46" s="12">
+        <f t="shared" si="66"/>
+        <v>-4.3397424144203001E-2</v>
+      </c>
       <c r="Q46" s="13"/>
       <c r="R46" s="13"/>
       <c r="S46" s="3"/>
@@ -5937,28 +6063,31 @@
         <f t="shared" si="71"/>
         <v>0.54168003518364394</v>
       </c>
-      <c r="P47" s="13"/>
+      <c r="P47" s="13">
+        <f t="shared" ref="P47" si="72">P29/P27</f>
+        <v>0.60517438300800075</v>
+      </c>
       <c r="Q47" s="13"/>
       <c r="R47" s="13"/>
       <c r="S47" s="3"/>
       <c r="T47" s="13">
-        <f t="shared" ref="T47:X47" si="72">T29/T27</f>
+        <f t="shared" ref="T47:X47" si="73">T29/T27</f>
         <v>0.5523454385052059</v>
       </c>
       <c r="U47" s="13">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.55873853063456436</v>
       </c>
       <c r="V47" s="13">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.55975891204642381</v>
       </c>
       <c r="W47" s="13">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.57675977289324243</v>
       </c>
       <c r="X47" s="13">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0.55389063929085669</v>
       </c>
       <c r="Y47" s="13">
@@ -5974,31 +6103,31 @@
         <v>0.56600544016716803</v>
       </c>
       <c r="AB47" s="13">
-        <f t="shared" ref="AB47:AH47" si="73">AB29/AB27</f>
+        <f t="shared" ref="AB47:AH47" si="74">AB29/AB27</f>
         <v>0</v>
       </c>
       <c r="AC47" s="13">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AD47" s="13">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AE47" s="13">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AF47" s="13">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AG47" s="13">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AH47" s="13">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
     </row>
@@ -6007,79 +6136,82 @@
         <v>34</v>
       </c>
       <c r="C48" s="13">
-        <f t="shared" ref="C48:J48" si="74">C32/C27</f>
+        <f t="shared" ref="C48:J48" si="75">C32/C27</f>
         <v>0.20062755148961001</v>
       </c>
       <c r="D48" s="13">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.21694033718622191</v>
       </c>
       <c r="E48" s="13">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.15339453720094828</v>
       </c>
       <c r="F48" s="13">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.28513592230889301</v>
       </c>
       <c r="G48" s="13">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.19586389731317669</v>
       </c>
       <c r="H48" s="13">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.22783982644181255</v>
       </c>
       <c r="I48" s="13">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.20472699506813638</v>
       </c>
       <c r="J48" s="13">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0.2885695322466002</v>
       </c>
       <c r="K48" s="13">
-        <f t="shared" ref="K48:L48" si="75">K32/K27</f>
+        <f t="shared" ref="K48:L48" si="76">K32/K27</f>
         <v>0.18502231446095171</v>
       </c>
       <c r="L48" s="13">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0.20743309788180747</v>
       </c>
       <c r="M48" s="13">
-        <f t="shared" ref="M48:O48" si="76">M32/M27</f>
+        <f t="shared" ref="M48:O48" si="77">M32/M27</f>
         <v>0.16987513250607977</v>
       </c>
       <c r="N48" s="13">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0.22310749749849007</v>
       </c>
       <c r="O48" s="13">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0.11205116679337253</v>
       </c>
-      <c r="P48" s="13"/>
+      <c r="P48" s="13">
+        <f t="shared" ref="P48" si="78">P32/P27</f>
+        <v>0.1877989643285749</v>
+      </c>
       <c r="Q48" s="13"/>
       <c r="R48" s="13"/>
       <c r="S48" s="3"/>
       <c r="T48" s="13">
-        <f t="shared" ref="T48:X48" si="77">T32/T27</f>
+        <f t="shared" ref="T48:X48" si="79">T32/T27</f>
         <v>0.21769086271739457</v>
       </c>
       <c r="U48" s="13">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>0.2234339943547802</v>
       </c>
       <c r="V48" s="13">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>0.18628090413207635</v>
       </c>
       <c r="W48" s="13">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>0.21311117493687085</v>
       </c>
       <c r="X48" s="13">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>0.163788305506504</v>
       </c>
       <c r="Y48" s="13">
@@ -6095,31 +6227,31 @@
         <v>0.19910786662583543</v>
       </c>
       <c r="AB48" s="13">
-        <f t="shared" ref="AB48:AH48" si="78">AB32/AB27</f>
+        <f t="shared" ref="AB48:AH48" si="80">AB32/AB27</f>
         <v>0</v>
       </c>
       <c r="AC48" s="13">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AD48" s="13">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AE48" s="13">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AF48" s="13">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AG48" s="13">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AH48" s="13">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
     </row>
@@ -6128,79 +6260,82 @@
         <v>35</v>
       </c>
       <c r="C49" s="13">
-        <f t="shared" ref="C49:J49" si="79">C36/C27</f>
+        <f t="shared" ref="C49:J49" si="81">C36/C27</f>
         <v>0.14514502257106174</v>
       </c>
       <c r="D49" s="13">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>0.15462991673324536</v>
       </c>
       <c r="E49" s="13">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>0.11283548178991361</v>
       </c>
       <c r="F49" s="13">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>0.20887565859817925</v>
       </c>
       <c r="G49" s="13">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>0.14551238607971156</v>
       </c>
       <c r="H49" s="13">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>0.16571449779383049</v>
       </c>
       <c r="I49" s="13">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>0.14681682007460373</v>
       </c>
       <c r="J49" s="13">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>0.20722791684445532</v>
       </c>
       <c r="K49" s="13">
-        <f t="shared" ref="K49:L49" si="80">K36/K27</f>
+        <f t="shared" ref="K49:L49" si="82">K36/K27</f>
         <v>0.13269384897032885</v>
       </c>
       <c r="L49" s="13">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>0.14688032998326084</v>
       </c>
       <c r="M49" s="13">
-        <f t="shared" ref="M49:O49" si="81">M36/M27</f>
+        <f t="shared" ref="M49:O49" si="83">M36/M27</f>
         <v>0.11958089106441359</v>
       </c>
       <c r="N49" s="13">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>0.16119282542495461</v>
       </c>
       <c r="O49" s="13">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>7.8915586362372878E-2</v>
       </c>
-      <c r="P49" s="13"/>
+      <c r="P49" s="13">
+        <f t="shared" ref="P49" si="84">P36/P27</f>
+        <v>0.13628861361689748</v>
+      </c>
       <c r="Q49" s="13"/>
       <c r="R49" s="13"/>
       <c r="S49" s="3"/>
       <c r="T49" s="13">
-        <f t="shared" ref="T49:X49" si="82">T36/T27</f>
+        <f t="shared" ref="T49:X49" si="85">T36/T27</f>
         <v>0.1501685207548295</v>
       </c>
       <c r="U49" s="13">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>0.16223874775839733</v>
       </c>
       <c r="V49" s="13">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>0.13378673062117341</v>
       </c>
       <c r="W49" s="13">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>0.15588647986603621</v>
       </c>
       <c r="X49" s="13">
-        <f t="shared" si="82"/>
+        <f t="shared" si="85"/>
         <v>0.10539400812623805</v>
       </c>
       <c r="Y49" s="13">
@@ -6216,31 +6351,31 @@
         <v>0.1422354223335075</v>
       </c>
       <c r="AB49" s="13">
-        <f t="shared" ref="AB49:AH49" si="83">AB36/AB27</f>
+        <f t="shared" ref="AB49:AH49" si="86">AB36/AB27</f>
         <v>0</v>
       </c>
       <c r="AC49" s="13">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="AD49" s="13">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="AE49" s="13">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="AF49" s="13">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="AG49" s="13">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="AH49" s="13">
-        <f t="shared" si="83"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
     </row>
@@ -6249,79 +6384,82 @@
         <v>36</v>
       </c>
       <c r="C50" s="13">
-        <f t="shared" ref="C50:J50" si="84">C35/C34</f>
+        <f t="shared" ref="C50:J50" si="87">C35/C34</f>
         <v>0.29072462564631135</v>
       </c>
       <c r="D50" s="13">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>0.29800727057513166</v>
       </c>
       <c r="E50" s="13">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>0.28521627672384825</v>
       </c>
       <c r="F50" s="13">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>0.28147082814579488</v>
       </c>
       <c r="G50" s="13">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>0.29501343422712056</v>
       </c>
       <c r="H50" s="13">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>0.29611622657733511</v>
       </c>
       <c r="I50" s="13">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>0.30240442185232486</v>
       </c>
       <c r="J50" s="13">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>0.29230904524513779</v>
       </c>
       <c r="K50" s="13">
-        <f t="shared" ref="K50:L50" si="85">K35/K34</f>
+        <f t="shared" ref="K50:L50" si="88">K35/K34</f>
         <v>0.30158899316402143</v>
       </c>
       <c r="L50" s="13">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>0.30483683846530135</v>
       </c>
       <c r="M50" s="13">
-        <f t="shared" ref="M50:O50" si="86">M35/M34</f>
+        <f t="shared" ref="M50:O50" si="89">M35/M34</f>
         <v>0.30539457599492903</v>
       </c>
       <c r="N50" s="13">
-        <f t="shared" si="86"/>
+        <f t="shared" si="89"/>
         <v>0.27837666689209539</v>
       </c>
       <c r="O50" s="13">
-        <f t="shared" si="86"/>
+        <f t="shared" si="89"/>
         <v>0.31819754821254431</v>
       </c>
-      <c r="P50" s="13"/>
+      <c r="P50" s="13">
+        <f t="shared" ref="P50" si="90">P35/P34</f>
+        <v>0.29555516089620026</v>
+      </c>
       <c r="Q50" s="13"/>
       <c r="R50" s="13"/>
       <c r="S50" s="3"/>
       <c r="T50" s="13">
-        <f t="shared" ref="T50:X50" si="87">T35/T34</f>
+        <f t="shared" ref="T50:X50" si="91">T35/T34</f>
         <v>0.319129515160958</v>
       </c>
       <c r="U50" s="13">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>0.28058721206873705</v>
       </c>
       <c r="V50" s="13">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>0.28124366876182338</v>
       </c>
       <c r="W50" s="13">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>0.2688022586925703</v>
       </c>
       <c r="X50" s="13">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>0.35853324138075948</v>
       </c>
       <c r="Y50" s="13">
@@ -6337,31 +6475,31 @@
         <v>0.29468232448267428</v>
       </c>
       <c r="AB50" s="13" t="e">
-        <f t="shared" ref="AB50:AH50" si="88">AB35/AB34</f>
+        <f t="shared" ref="AB50:AH50" si="92">AB35/AB34</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AC50" s="13" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="92"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD50" s="13" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="92"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AE50" s="13" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="92"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AF50" s="13" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="92"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AG50" s="13" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="92"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AH50" s="13" t="e">
-        <f t="shared" si="88"/>
+        <f t="shared" si="92"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -6643,27 +6781,27 @@
       <c r="R57" s="3"/>
       <c r="S57" s="3"/>
       <c r="T57" s="3">
-        <f t="shared" ref="T57:V57" si="89">+SUM(T52:T56)</f>
+        <f t="shared" ref="T57:V57" si="93">+SUM(T52:T56)</f>
         <v>1429.2819999999999</v>
       </c>
       <c r="U57" s="3">
-        <f t="shared" si="89"/>
+        <f t="shared" si="93"/>
         <v>1807.9380000000001</v>
       </c>
       <c r="V57" s="3">
-        <f t="shared" si="89"/>
+        <f t="shared" si="93"/>
         <v>2124.3790000000004</v>
       </c>
       <c r="W57" s="3">
-        <f t="shared" ref="W57:Y57" si="90">+SUM(W52:W56)</f>
+        <f t="shared" ref="W57:Y57" si="94">+SUM(W52:W56)</f>
         <v>2614.8530000000001</v>
       </c>
       <c r="X57" s="3">
-        <f t="shared" si="90"/>
+        <f t="shared" si="94"/>
         <v>3159.453</v>
       </c>
       <c r="Y57" s="3">
-        <f t="shared" si="90"/>
+        <f t="shared" si="94"/>
         <v>4060.5769999999998</v>
       </c>
       <c r="Z57" s="3">
@@ -7120,27 +7258,27 @@
       <c r="R64" s="3"/>
       <c r="S64" s="3"/>
       <c r="T64" s="3">
-        <f t="shared" ref="T64:W64" si="91">+SUM(T58:T63)</f>
+        <f t="shared" ref="T64:W64" si="95">+SUM(T58:T63)</f>
         <v>655.42899999999997</v>
       </c>
       <c r="U64" s="3">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>1473.4169999999999</v>
       </c>
       <c r="V64" s="3">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>2060.8359999999998</v>
       </c>
       <c r="W64" s="3">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>2327.625</v>
       </c>
       <c r="X64" s="3">
-        <f t="shared" ref="X64:Y64" si="92">+SUM(X58:X63)</f>
+        <f t="shared" ref="X64:Y64" si="96">+SUM(X58:X63)</f>
         <v>2447.5849999999996</v>
       </c>
       <c r="Y64" s="3">
-        <f t="shared" si="92"/>
+        <f t="shared" si="96"/>
         <v>3031.364</v>
       </c>
       <c r="Z64" s="3">
@@ -7195,27 +7333,27 @@
       <c r="R65" s="3"/>
       <c r="S65" s="3"/>
       <c r="T65" s="11">
-        <f t="shared" ref="T65:W65" si="93">+T64+T57</f>
+        <f t="shared" ref="T65:W65" si="97">+T64+T57</f>
         <v>2084.7109999999998</v>
       </c>
       <c r="U65" s="11">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>3281.355</v>
       </c>
       <c r="V65" s="11">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>4185.2150000000001</v>
       </c>
       <c r="W65" s="11">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>4942.4780000000001</v>
       </c>
       <c r="X65" s="11">
-        <f t="shared" ref="X65:Y65" si="94">+X64+X57</f>
+        <f t="shared" ref="X65:Y65" si="98">+X64+X57</f>
         <v>5607.0379999999996</v>
       </c>
       <c r="Y65" s="11">
-        <f t="shared" si="94"/>
+        <f t="shared" si="98"/>
         <v>7091.9409999999998</v>
       </c>
       <c r="Z65" s="11">
@@ -7741,27 +7879,27 @@
       <c r="R73" s="3"/>
       <c r="S73" s="3"/>
       <c r="T73" s="3">
-        <f t="shared" ref="T73:W73" si="95">+SUM(T66:T72)</f>
+        <f t="shared" ref="T73:W73" si="99">+SUM(T66:T72)</f>
         <v>500.47699999999998</v>
       </c>
       <c r="U73" s="3">
-        <f t="shared" si="95"/>
+        <f t="shared" si="99"/>
         <v>620.41800000000001</v>
       </c>
       <c r="V73" s="3">
-        <f t="shared" si="95"/>
+        <f t="shared" si="99"/>
         <v>883.17799999999988</v>
       </c>
       <c r="W73" s="3">
-        <f t="shared" si="95"/>
+        <f t="shared" si="99"/>
         <v>1405.3340000000001</v>
       </c>
       <c r="X73" s="3">
-        <f t="shared" ref="X73:Y73" si="96">+SUM(X66:X72)</f>
+        <f t="shared" ref="X73:Y73" si="100">+SUM(X66:X72)</f>
         <v>1492.1980000000001</v>
       </c>
       <c r="Y73" s="3">
-        <f t="shared" si="96"/>
+        <f t="shared" si="100"/>
         <v>1631.261</v>
       </c>
       <c r="Z73" s="3">
@@ -8084,19 +8222,19 @@
       <c r="R78" s="3"/>
       <c r="S78" s="3"/>
       <c r="T78" s="3">
-        <f t="shared" ref="T78:W78" si="97">+SUM(T74:T77)</f>
+        <f t="shared" ref="T78:W78" si="101">+SUM(T74:T77)</f>
         <v>138.25900000000001</v>
       </c>
       <c r="U78" s="3">
-        <f t="shared" si="97"/>
+        <f t="shared" si="101"/>
         <v>708.71800000000007</v>
       </c>
       <c r="V78" s="3">
-        <f t="shared" si="97"/>
+        <f t="shared" si="101"/>
         <v>743.471</v>
       </c>
       <c r="W78" s="3">
-        <f t="shared" si="97"/>
+        <f t="shared" si="101"/>
         <v>797.09799999999996</v>
       </c>
       <c r="X78" s="3">
@@ -8226,27 +8364,27 @@
       <c r="R80" s="3"/>
       <c r="S80" s="3"/>
       <c r="T80" s="11">
-        <f t="shared" ref="T80:W80" si="98">+T79+T78+T73</f>
+        <f t="shared" ref="T80:W80" si="102">+T79+T78+T73</f>
         <v>2084.7109999999998</v>
       </c>
       <c r="U80" s="11">
-        <f t="shared" si="98"/>
+        <f t="shared" si="102"/>
         <v>3281.3540000000003</v>
       </c>
       <c r="V80" s="11">
-        <f t="shared" si="98"/>
+        <f t="shared" si="102"/>
         <v>4185.2150000000001</v>
       </c>
       <c r="W80" s="11">
-        <f t="shared" si="98"/>
+        <f t="shared" si="102"/>
         <v>4942.4780000000001</v>
       </c>
       <c r="X80" s="11">
-        <f t="shared" ref="X80:Y80" si="99">+X79+X78+X73</f>
+        <f t="shared" ref="X80:Y80" si="103">+X79+X78+X73</f>
         <v>5607.0380000000005</v>
       </c>
       <c r="Y80" s="11">
-        <f t="shared" si="99"/>
+        <f t="shared" si="103"/>
         <v>7091.9410000000007</v>
       </c>
       <c r="Z80" s="11">
@@ -8361,11 +8499,11 @@
         <v>975.322</v>
       </c>
       <c r="X82" s="3">
-        <f t="shared" ref="X82:Y82" si="100">+X36</f>
+        <f t="shared" ref="X82:Y82" si="104">+X36</f>
         <v>854.8</v>
       </c>
       <c r="Y82" s="3">
-        <f t="shared" si="100"/>
+        <f t="shared" si="104"/>
         <v>1550.190000000001</v>
       </c>
       <c r="Z82" s="3">
@@ -9629,27 +9767,27 @@
       <c r="R101" s="3"/>
       <c r="S101" s="3"/>
       <c r="T101" s="3">
-        <f t="shared" ref="T101:Y101" si="101">+SUM(T89:T100)</f>
+        <f t="shared" ref="T101:Y101" si="105">+SUM(T89:T100)</f>
         <v>112.87500000000003</v>
       </c>
       <c r="U101" s="3">
-        <f t="shared" si="101"/>
+        <f t="shared" si="105"/>
         <v>-194.07099999999997</v>
       </c>
       <c r="V101" s="3">
-        <f t="shared" si="101"/>
+        <f t="shared" si="105"/>
         <v>-47.549000000000014</v>
       </c>
       <c r="W101" s="3">
-        <f t="shared" si="101"/>
+        <f t="shared" si="105"/>
         <v>129.13100000000006</v>
       </c>
       <c r="X101" s="3">
-        <f t="shared" si="101"/>
+        <f t="shared" si="105"/>
         <v>-659.91999999999985</v>
       </c>
       <c r="Y101" s="3">
-        <f t="shared" si="101"/>
+        <f t="shared" si="105"/>
         <v>199.22299999999998</v>
       </c>
       <c r="Z101" s="3">
@@ -9704,27 +9842,27 @@
       <c r="R102" s="3"/>
       <c r="S102" s="3"/>
       <c r="T102" s="11">
-        <f t="shared" ref="T102:Y102" si="102">+SUM(T101,T82:T88)</f>
+        <f t="shared" ref="T102:Y102" si="106">+SUM(T101,T82:T88)</f>
         <v>742.779</v>
       </c>
       <c r="U102" s="11">
-        <f t="shared" si="102"/>
+        <f t="shared" si="106"/>
         <v>669.31600000000014</v>
       </c>
       <c r="V102" s="11">
-        <f t="shared" si="102"/>
+        <f t="shared" si="106"/>
         <v>803.3370000000001</v>
       </c>
       <c r="W102" s="11">
-        <f t="shared" si="102"/>
+        <f t="shared" si="106"/>
         <v>1389.1079999999997</v>
       </c>
       <c r="X102" s="11">
-        <f t="shared" si="102"/>
+        <f t="shared" si="106"/>
         <v>966.46300000000019</v>
       </c>
       <c r="Y102" s="11">
-        <f t="shared" si="102"/>
+        <f t="shared" si="106"/>
         <v>2296.1640000000011</v>
       </c>
       <c r="Z102" s="11">
@@ -10047,27 +10185,27 @@
       <c r="R107" s="3"/>
       <c r="S107" s="3"/>
       <c r="T107" s="11">
-        <f t="shared" ref="T107:Y107" si="103">+SUM(T103:T106)</f>
+        <f t="shared" ref="T107:Y107" si="107">+SUM(T103:T106)</f>
         <v>-242.79399999999998</v>
       </c>
       <c r="U107" s="11">
-        <f t="shared" si="103"/>
+        <f t="shared" si="107"/>
         <v>-278.40800000000002</v>
       </c>
       <c r="V107" s="11">
-        <f t="shared" si="103"/>
+        <f t="shared" si="107"/>
         <v>-695.53200000000004</v>
       </c>
       <c r="W107" s="11">
-        <f t="shared" si="103"/>
+        <f t="shared" si="107"/>
         <v>-427.89100000000002</v>
       </c>
       <c r="X107" s="11">
-        <f t="shared" si="103"/>
+        <f t="shared" si="107"/>
         <v>-569.93700000000001</v>
       </c>
       <c r="Y107" s="11">
-        <f t="shared" si="103"/>
+        <f t="shared" si="107"/>
         <v>-654.13200000000006</v>
       </c>
       <c r="Z107" s="11">
@@ -10390,27 +10528,27 @@
       <c r="R112" s="3"/>
       <c r="S112" s="11"/>
       <c r="T112" s="11">
-        <f t="shared" ref="T112:Y112" si="104">+SUM(T108:T111)</f>
+        <f t="shared" ref="T112:Y112" si="108">+SUM(T108:T111)</f>
         <v>-590.21400000000006</v>
       </c>
       <c r="U112" s="11">
-        <f t="shared" si="104"/>
+        <f t="shared" si="108"/>
         <v>-177.173</v>
       </c>
       <c r="V112" s="11">
-        <f t="shared" si="104"/>
+        <f t="shared" si="108"/>
         <v>-80.787999999999997</v>
       </c>
       <c r="W112" s="11">
-        <f t="shared" si="104"/>
+        <f t="shared" si="108"/>
         <v>-844.98699999999997</v>
       </c>
       <c r="X112" s="11">
-        <f t="shared" si="104"/>
+        <f t="shared" si="108"/>
         <v>-467.48699999999997</v>
       </c>
       <c r="Y112" s="11">
-        <f t="shared" si="104"/>
+        <f t="shared" si="108"/>
         <v>-548.82800000000009</v>
       </c>
       <c r="Z112" s="11">
@@ -10532,27 +10670,27 @@
       <c r="R114" s="3"/>
       <c r="S114" s="3"/>
       <c r="T114" s="3">
-        <f t="shared" ref="T114:Y114" si="105">+SUM(T112,T113,T107,T102)</f>
+        <f t="shared" ref="T114:Y114" si="109">+SUM(T112,T113,T107,T102)</f>
         <v>-109.18100000000004</v>
       </c>
       <c r="U114" s="3">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>212.18500000000012</v>
       </c>
       <c r="V114" s="3">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>57.013000000000034</v>
       </c>
       <c r="W114" s="3">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>109.35399999999981</v>
       </c>
       <c r="X114" s="3">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>-105.00399999999991</v>
       </c>
       <c r="Y114" s="3">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>1089.104000000001</v>
       </c>
       <c r="Z114" s="3">
@@ -10679,27 +10817,27 @@
       <c r="R116" s="3"/>
       <c r="S116" s="3"/>
       <c r="T116" s="3">
-        <f t="shared" ref="T116:Y116" si="106">+U115</f>
+        <f t="shared" ref="T116:Y116" si="110">+U115</f>
         <v>881.31900000000019</v>
       </c>
       <c r="U116" s="3">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>1093.5040000000004</v>
       </c>
       <c r="V116" s="3">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>1150.5170000000003</v>
       </c>
       <c r="W116" s="3">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>1259.8710000000001</v>
       </c>
       <c r="X116" s="3">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>1154.867</v>
       </c>
       <c r="Y116" s="3">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>2243.971</v>
       </c>
       <c r="Z116" s="3">
@@ -10850,31 +10988,31 @@
       <c r="R119" s="3"/>
       <c r="S119" s="3"/>
       <c r="T119" s="3">
-        <f t="shared" ref="T119:W119" si="107">+T102+T103</f>
+        <f t="shared" ref="T119:W119" si="111">+T102+T103</f>
         <v>516.97199999999998</v>
       </c>
       <c r="U119" s="3">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>386.26800000000014</v>
       </c>
       <c r="V119" s="3">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>574.1110000000001</v>
       </c>
       <c r="W119" s="3">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>994.60599999999977</v>
       </c>
       <c r="X119" s="3">
-        <f t="shared" ref="X119:Z119" si="108">+X102+X103</f>
+        <f t="shared" ref="X119:Z119" si="112">+X102+X103</f>
         <v>327.80600000000015</v>
       </c>
       <c r="Y119" s="3">
-        <f t="shared" si="108"/>
+        <f t="shared" si="112"/>
         <v>1644.2990000000011</v>
       </c>
       <c r="Z119" s="3">
-        <f t="shared" si="108"/>
+        <f t="shared" si="112"/>
         <v>1583.4810000000007</v>
       </c>
       <c r="AA119" s="3">
@@ -20940,7 +21078,7 @@
       </c>
       <c r="K3" s="24">
         <f>+Main!I2</f>
-        <v>110.86</v>
+        <v>99.65</v>
       </c>
       <c r="L3" s="20"/>
       <c r="M3" s="20"/>
@@ -20991,7 +21129,7 @@
       </c>
       <c r="K4" s="24">
         <f>+Main!I3</f>
-        <v>108.437957</v>
+        <v>105.594064</v>
       </c>
       <c r="L4" s="20"/>
       <c r="M4" s="20"/>
@@ -21042,7 +21180,7 @@
       </c>
       <c r="K5" s="24">
         <f>+K3*K4</f>
-        <v>12021.43191302</v>
+        <v>10522.448477600001</v>
       </c>
       <c r="L5" s="20"/>
       <c r="M5" s="20"/>
@@ -21093,7 +21231,7 @@
       </c>
       <c r="K6" s="24">
         <f>+Main!I6-Main!I5</f>
-        <v>-1514.729</v>
+        <v>-189.73699999999999</v>
       </c>
       <c r="L6" s="20"/>
       <c r="M6" s="20"/>
@@ -21144,7 +21282,7 @@
       </c>
       <c r="K7" s="24">
         <f>+K5+K6</f>
-        <v>10506.702913020001</v>
+        <v>10332.711477600002</v>
       </c>
       <c r="L7" s="20"/>
       <c r="M7" s="20"/>
@@ -22906,7 +23044,7 @@
       <c r="I3" s="20"/>
       <c r="J3" s="39">
         <f>+Main!I2</f>
-        <v>110.86</v>
+        <v>99.65</v>
       </c>
       <c r="K3" s="20"/>
       <c r="L3" s="20" t="s">
@@ -22916,7 +23054,7 @@
       <c r="N3" s="20"/>
       <c r="O3" s="39">
         <f>+J3</f>
-        <v>110.86</v>
+        <v>99.65</v>
       </c>
       <c r="P3" s="20"/>
       <c r="Q3" s="20"/>
@@ -22944,7 +23082,7 @@
       <c r="D4" s="20"/>
       <c r="E4" s="40">
         <f ca="1">+TODAY()</f>
-        <v>46239</v>
+        <v>46269</v>
       </c>
       <c r="F4" s="20"/>
       <c r="G4" s="20" t="s">
@@ -22954,7 +23092,7 @@
       <c r="I4" s="20"/>
       <c r="J4" s="41">
         <f ca="1">V62</f>
-        <v>214.26906862817964</v>
+        <v>185.21581224575729</v>
       </c>
       <c r="K4" s="20"/>
       <c r="L4" s="20" t="s">
@@ -23001,7 +23139,7 @@
       <c r="I5" s="20"/>
       <c r="J5" s="44">
         <f ca="1">J4/J3-1</f>
-        <v>0.93278972242630021</v>
+        <v>0.85866344451336962</v>
       </c>
       <c r="K5" s="20"/>
       <c r="L5" s="20" t="s">
@@ -23235,7 +23373,7 @@
       <c r="C11" s="20"/>
       <c r="D11" s="20"/>
       <c r="E11" s="43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="20"/>
       <c r="G11" s="20" t="s">
@@ -23868,43 +24006,43 @@
       </c>
       <c r="M25" s="24">
         <f ca="1">L25*(1+M26)</f>
-        <v>11435.678</v>
+        <v>11102.6</v>
       </c>
       <c r="N25" s="24">
         <f t="shared" ref="N25:V25" ca="1" si="1">M25*(1+N26)</f>
-        <v>11571.07642752</v>
+        <v>11102.6</v>
       </c>
       <c r="O25" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>11708.077972421837</v>
+        <v>11102.6</v>
       </c>
       <c r="P25" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>11846.701615615309</v>
+        <v>11102.6</v>
       </c>
       <c r="Q25" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>11986.966562744195</v>
+        <v>11102.6</v>
       </c>
       <c r="R25" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>12128.892246847088</v>
+        <v>11102.6</v>
       </c>
       <c r="S25" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>12272.498331049759</v>
+        <v>11102.6</v>
       </c>
       <c r="T25" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>12419.768311022357</v>
+        <v>11102.6</v>
       </c>
       <c r="U25" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>12568.805530754626</v>
+        <v>11102.6</v>
       </c>
       <c r="V25" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>12719.631197123681</v>
+        <v>11102.6</v>
       </c>
       <c r="W25" s="20"/>
       <c r="X25" s="20"/>
@@ -23948,43 +24086,43 @@
       </c>
       <c r="M26" s="55" cm="1">
         <f t="array" aca="1" ref="M26" ca="1">OFFSET(M26,$E$11,,)</f>
-        <v>3.0000000000000027E-2</v>
+        <v>0</v>
       </c>
       <c r="N26" s="55" cm="1">
         <f t="array" aca="1" ref="N26" ca="1">OFFSET(N26,$E$11,,)</f>
-        <v>1.1840000000000073E-2</v>
+        <v>0</v>
       </c>
       <c r="O26" s="55" cm="1">
         <f t="array" aca="1" ref="O26" ca="1">OFFSET(O26,$E$11,,)</f>
-        <v>1.1840000000000073E-2</v>
+        <v>0</v>
       </c>
       <c r="P26" s="55" cm="1">
         <f t="array" aca="1" ref="P26" ca="1">OFFSET(P26,$E$11,,)</f>
-        <v>1.1839999999999851E-2</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="55" cm="1">
         <f t="array" aca="1" ref="Q26" ca="1">OFFSET(Q26,$E$11,,)</f>
-        <v>1.1840000000000073E-2</v>
+        <v>0</v>
       </c>
       <c r="R26" s="55" cm="1">
         <f t="array" aca="1" ref="R26" ca="1">OFFSET(R26,$E$11,,)</f>
-        <v>1.1840000000000073E-2</v>
+        <v>0</v>
       </c>
       <c r="S26" s="55" cm="1">
         <f t="array" aca="1" ref="S26" ca="1">OFFSET(S26,$E$11,,)</f>
-        <v>1.1840000000000073E-2</v>
+        <v>0</v>
       </c>
       <c r="T26" s="55" cm="1">
         <f t="array" aca="1" ref="T26" ca="1">OFFSET(T26,$E$11,,)</f>
-        <v>1.2E-2</v>
+        <v>0</v>
       </c>
       <c r="U26" s="55" cm="1">
         <f t="array" aca="1" ref="U26" ca="1">OFFSET(U26,$E$11,,)</f>
-        <v>1.2E-2</v>
+        <v>0</v>
       </c>
       <c r="V26" s="55" cm="1">
         <f t="array" aca="1" ref="V26" ca="1">OFFSET(V26,$E$11,,)</f>
-        <v>1.2E-2</v>
+        <v>0</v>
       </c>
       <c r="W26" s="20"/>
       <c r="X26" s="20"/>
@@ -24216,43 +24354,43 @@
       </c>
       <c r="M31" s="24">
         <f ca="1">M32*M25</f>
-        <v>1486.63814</v>
+        <v>1443.3380000000002</v>
       </c>
       <c r="N31" s="24">
         <f t="shared" ref="N31:V31" ca="1" si="3">N32*N25</f>
-        <v>2082.7937569535998</v>
+        <v>1998.4680000000001</v>
       </c>
       <c r="O31" s="24">
         <f t="shared" ca="1" si="3"/>
-        <v>2224.5348147601489</v>
+        <v>2109.4940000000001</v>
       </c>
       <c r="P31" s="24">
         <f t="shared" ca="1" si="3"/>
-        <v>2369.3403231230618</v>
+        <v>2220.52</v>
       </c>
       <c r="Q31" s="24">
         <f t="shared" ca="1" si="3"/>
-        <v>2517.2629781762807</v>
+        <v>2331.5459999999998</v>
       </c>
       <c r="R31" s="24">
         <f t="shared" ca="1" si="3"/>
-        <v>2668.3562943063594</v>
+        <v>2442.5720000000001</v>
       </c>
       <c r="S31" s="24">
         <f t="shared" ca="1" si="3"/>
-        <v>2822.6746161414449</v>
+        <v>2553.5980000000004</v>
       </c>
       <c r="T31" s="24">
         <f t="shared" ca="1" si="3"/>
-        <v>2980.7443946453654</v>
+        <v>2664.6239999999998</v>
       </c>
       <c r="U31" s="24">
         <f t="shared" ca="1" si="3"/>
-        <v>3142.2013826886564</v>
+        <v>2775.65</v>
       </c>
       <c r="V31" s="24">
         <f t="shared" ca="1" si="3"/>
-        <v>3179.9077992809202</v>
+        <v>2775.65</v>
       </c>
       <c r="W31" s="20"/>
       <c r="X31" s="20"/>
@@ -24560,43 +24698,43 @@
       </c>
       <c r="M37" s="24">
         <f ca="1">M38*M31</f>
-        <v>431.12506059999998</v>
+        <v>418.56802000000005</v>
       </c>
       <c r="N37" s="24">
         <f t="shared" ref="N37:V37" ca="1" si="5">N38*N31</f>
-        <v>604.01018951654385</v>
+        <v>579.55571999999995</v>
       </c>
       <c r="O37" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>645.11509628044314</v>
+        <v>611.75325999999995</v>
       </c>
       <c r="P37" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>687.10869370568787</v>
+        <v>643.95079999999996</v>
       </c>
       <c r="Q37" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>730.00626367112136</v>
+        <v>676.14833999999985</v>
       </c>
       <c r="R37" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>773.82332534884415</v>
+        <v>708.34587999999997</v>
       </c>
       <c r="S37" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>818.57563868101897</v>
+        <v>740.54342000000008</v>
       </c>
       <c r="T37" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>864.41587444715594</v>
+        <v>772.74095999999986</v>
       </c>
       <c r="U37" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>911.23840097971026</v>
+        <v>804.93849999999998</v>
       </c>
       <c r="V37" s="24">
         <f t="shared" ca="1" si="5"/>
-        <v>922.17326179146676</v>
+        <v>804.93849999999998</v>
       </c>
       <c r="W37" s="20"/>
       <c r="X37" s="20"/>
@@ -24749,43 +24887,43 @@
       </c>
       <c r="M40" s="59">
         <f t="shared" ca="1" si="7"/>
-        <v>1055.5130794000002</v>
+        <v>1024.76998</v>
       </c>
       <c r="N40" s="59">
         <f t="shared" ca="1" si="7"/>
-        <v>1478.7835674370558</v>
+        <v>1418.91228</v>
       </c>
       <c r="O40" s="59">
         <f t="shared" ca="1" si="7"/>
-        <v>1579.4197184797058</v>
+        <v>1497.7407400000002</v>
       </c>
       <c r="P40" s="59">
         <f t="shared" ca="1" si="7"/>
-        <v>1682.2316294173738</v>
+        <v>1576.5691999999999</v>
       </c>
       <c r="Q40" s="59">
         <f t="shared" ca="1" si="7"/>
-        <v>1787.2567145051594</v>
+        <v>1655.3976600000001</v>
       </c>
       <c r="R40" s="59">
         <f t="shared" ca="1" si="7"/>
-        <v>1894.5329689575151</v>
+        <v>1734.2261200000003</v>
       </c>
       <c r="S40" s="59">
         <f t="shared" ca="1" si="7"/>
-        <v>2004.0989774604259</v>
+        <v>1813.0545800000004</v>
       </c>
       <c r="T40" s="59">
         <f t="shared" ca="1" si="7"/>
-        <v>2116.3285201982094</v>
+        <v>1891.8830399999999</v>
       </c>
       <c r="U40" s="59">
         <f t="shared" ca="1" si="7"/>
-        <v>2230.9629817089462</v>
+        <v>1970.7115000000001</v>
       </c>
       <c r="V40" s="60">
         <f t="shared" ca="1" si="7"/>
-        <v>2257.7345374894535</v>
+        <v>1970.7115000000001</v>
       </c>
       <c r="W40" s="20"/>
       <c r="X40" s="20"/>
@@ -24865,43 +25003,43 @@
       </c>
       <c r="M42" s="24">
         <f ca="1">M43*M25</f>
-        <v>514.60550999999998</v>
+        <v>499.61700000000002</v>
       </c>
       <c r="N42" s="24">
         <f t="shared" ref="N42:V42" ca="1" si="8">N43*N25</f>
-        <v>520.69843923839994</v>
+        <v>499.61700000000002</v>
       </c>
       <c r="O42" s="24">
         <f t="shared" ca="1" si="8"/>
-        <v>526.86350875898268</v>
+        <v>499.61700000000002</v>
       </c>
       <c r="P42" s="24">
         <f t="shared" ca="1" si="8"/>
-        <v>533.10157270268894</v>
+        <v>499.61700000000002</v>
       </c>
       <c r="Q42" s="24">
         <f t="shared" ca="1" si="8"/>
-        <v>539.41349532348875</v>
+        <v>499.61700000000002</v>
       </c>
       <c r="R42" s="24">
         <f t="shared" ca="1" si="8"/>
-        <v>545.80015110811894</v>
+        <v>499.61700000000002</v>
       </c>
       <c r="S42" s="24">
         <f t="shared" ca="1" si="8"/>
-        <v>552.26242489723916</v>
+        <v>499.61700000000002</v>
       </c>
       <c r="T42" s="24">
         <f t="shared" ca="1" si="8"/>
-        <v>558.88957399600599</v>
+        <v>499.61700000000002</v>
       </c>
       <c r="U42" s="24">
         <f t="shared" ca="1" si="8"/>
-        <v>565.59624888395808</v>
+        <v>499.61700000000002</v>
       </c>
       <c r="V42" s="24">
         <f t="shared" ca="1" si="8"/>
-        <v>572.38340387056564</v>
+        <v>499.61700000000002</v>
       </c>
       <c r="W42" s="20"/>
       <c r="X42" s="20"/>
@@ -25054,43 +25192,43 @@
       </c>
       <c r="M45" s="24">
         <f ca="1">M46*M25</f>
-        <v>-800.49746000000005</v>
+        <v>-777.18200000000013</v>
       </c>
       <c r="N45" s="24">
         <f t="shared" ref="N45:V45" ca="1" si="10">N46*N25</f>
-        <v>-809.9753499264001</v>
+        <v>-777.18200000000013</v>
       </c>
       <c r="O45" s="24">
         <f t="shared" ca="1" si="10"/>
-        <v>-819.56545806952874</v>
+        <v>-777.18200000000013</v>
       </c>
       <c r="P45" s="24">
         <f t="shared" ca="1" si="10"/>
-        <v>-829.26911309307172</v>
+        <v>-777.18200000000013</v>
       </c>
       <c r="Q45" s="24">
         <f t="shared" ca="1" si="10"/>
-        <v>-839.08765939209377</v>
+        <v>-777.18200000000013</v>
       </c>
       <c r="R45" s="24">
         <f t="shared" ca="1" si="10"/>
-        <v>-849.0224572792963</v>
+        <v>-777.18200000000013</v>
       </c>
       <c r="S45" s="24">
         <f t="shared" ca="1" si="10"/>
-        <v>-859.07488317348327</v>
+        <v>-777.18200000000013</v>
       </c>
       <c r="T45" s="24">
         <f t="shared" ca="1" si="10"/>
-        <v>-869.38378177156505</v>
+        <v>-777.18200000000013</v>
       </c>
       <c r="U45" s="24">
         <f t="shared" ca="1" si="10"/>
-        <v>-879.81638715282384</v>
+        <v>-777.18200000000013</v>
       </c>
       <c r="V45" s="24">
         <f t="shared" ca="1" si="10"/>
-        <v>-890.37418379865778</v>
+        <v>-777.18200000000013</v>
       </c>
       <c r="W45" s="20"/>
       <c r="X45" s="20"/>
@@ -25243,43 +25381,43 @@
       </c>
       <c r="M48" s="24">
         <f ca="1">M49*M25</f>
-        <v>-343.07033999999999</v>
+        <v>-333.07799999999997</v>
       </c>
       <c r="N48" s="24">
         <f t="shared" ref="N48:V48" ca="1" si="12">N49*N25</f>
-        <v>-347.13229282559996</v>
+        <v>-333.07799999999997</v>
       </c>
       <c r="O48" s="24">
         <f t="shared" ca="1" si="12"/>
-        <v>-351.24233917265508</v>
+        <v>-333.07799999999997</v>
       </c>
       <c r="P48" s="24">
         <f t="shared" ca="1" si="12"/>
-        <v>-355.40104846845929</v>
+        <v>-333.07799999999997</v>
       </c>
       <c r="Q48" s="24">
         <f t="shared" ca="1" si="12"/>
-        <v>-359.60899688232587</v>
+        <v>-333.07799999999997</v>
       </c>
       <c r="R48" s="24">
         <f t="shared" ca="1" si="12"/>
-        <v>-363.86676740541265</v>
+        <v>-333.07799999999997</v>
       </c>
       <c r="S48" s="24">
         <f t="shared" ca="1" si="12"/>
-        <v>-368.17494993149273</v>
+        <v>-333.07799999999997</v>
       </c>
       <c r="T48" s="24">
         <f t="shared" ca="1" si="12"/>
-        <v>-372.59304933067068</v>
+        <v>-333.07799999999997</v>
       </c>
       <c r="U48" s="24">
         <f t="shared" ca="1" si="12"/>
-        <v>-377.06416592263878</v>
+        <v>-333.07799999999997</v>
       </c>
       <c r="V48" s="24">
         <f t="shared" ca="1" si="12"/>
-        <v>-381.58893591371043</v>
+        <v>-333.07799999999997</v>
       </c>
       <c r="W48" s="20"/>
       <c r="X48" s="20"/>
@@ -25432,43 +25570,43 @@
       </c>
       <c r="M51" s="65">
         <f ca="1">M40+M42+M45+M48</f>
-        <v>426.55078939999999</v>
+        <v>414.12697999999989</v>
       </c>
       <c r="N51" s="65">
         <f t="shared" ca="1" si="14"/>
-        <v>842.3743639234558</v>
+        <v>808.26927999999998</v>
       </c>
       <c r="O51" s="65">
         <f t="shared" ca="1" si="14"/>
-        <v>935.47542999650489</v>
+        <v>887.09774000000016</v>
       </c>
       <c r="P51" s="65">
         <f t="shared" ca="1" si="14"/>
-        <v>1030.6630405585317</v>
+        <v>965.92619999999988</v>
       </c>
       <c r="Q51" s="65">
         <f t="shared" ca="1" si="14"/>
-        <v>1127.9735535542286</v>
+        <v>1044.7546600000001</v>
       </c>
       <c r="R51" s="65">
         <f t="shared" ca="1" si="14"/>
-        <v>1227.4438953809249</v>
+        <v>1123.5831200000002</v>
       </c>
       <c r="S51" s="65">
         <f t="shared" ca="1" si="14"/>
-        <v>1329.1115692526892</v>
+        <v>1202.4115800000004</v>
       </c>
       <c r="T51" s="65">
         <f t="shared" ca="1" si="14"/>
-        <v>1433.2412630919794</v>
+        <v>1281.2400399999997</v>
       </c>
       <c r="U51" s="65">
         <f t="shared" ca="1" si="14"/>
-        <v>1539.6786775174419</v>
+        <v>1360.0684999999999</v>
       </c>
       <c r="V51" s="66">
         <f ca="1">V40+V42+V45+V48</f>
-        <v>1558.1548216476513</v>
+        <v>1360.0684999999999</v>
       </c>
       <c r="W51" s="20"/>
       <c r="X51" s="20"/>
@@ -25497,43 +25635,43 @@
       <c r="L52" s="69"/>
       <c r="M52" s="69">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>199.73705354807424</v>
+        <v>162.79036263424092</v>
       </c>
       <c r="N52" s="69">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>751.33518453106956</v>
+        <v>725.39929240716026</v>
       </c>
       <c r="O52" s="69">
         <f t="shared" ref="O52:U52" ca="1" si="15">O51/(1+$E$18)^O53</f>
-        <v>772.56888926996612</v>
+        <v>737.17189997115531</v>
       </c>
       <c r="P52" s="69">
         <f t="shared" ca="1" si="15"/>
-        <v>788.12985129497793</v>
+        <v>743.22017449462851</v>
       </c>
       <c r="Q52" s="69">
         <f t="shared" ca="1" si="15"/>
-        <v>798.64952268942761</v>
+        <v>744.32756939064029</v>
       </c>
       <c r="R52" s="69">
         <f t="shared" ca="1" si="15"/>
-        <v>804.702246855716</v>
+        <v>741.19288013473454</v>
       </c>
       <c r="S52" s="69">
         <f t="shared" ca="1" si="15"/>
-        <v>806.80995181849539</v>
+        <v>734.43848739745056</v>
       </c>
       <c r="T52" s="69">
         <f t="shared" ca="1" si="15"/>
-        <v>805.57384204654898</v>
+        <v>724.61784348744686</v>
       </c>
       <c r="U52" s="69">
         <f t="shared" ca="1" si="15"/>
-        <v>801.29492584978766</v>
+        <v>712.22226897756786</v>
       </c>
       <c r="V52" s="70">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>750.8430231110973</v>
+        <v>659.46506386811836</v>
       </c>
       <c r="W52" s="20"/>
       <c r="X52" s="20"/>
@@ -25562,43 +25700,43 @@
       <c r="L53" s="20"/>
       <c r="M53" s="32">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.4861111111111111</v>
+        <v>0.40555555555555556</v>
       </c>
       <c r="N53" s="32">
         <f ca="1">M53+1</f>
-        <v>1.4861111111111112</v>
+        <v>1.4055555555555554</v>
       </c>
       <c r="O53" s="32">
         <f ca="1">N53+1</f>
-        <v>2.4861111111111112</v>
+        <v>2.4055555555555554</v>
       </c>
       <c r="P53" s="32">
         <f t="shared" ref="P53:V53" ca="1" si="16">O53+1</f>
-        <v>3.4861111111111112</v>
+        <v>3.4055555555555554</v>
       </c>
       <c r="Q53" s="32">
         <f t="shared" ca="1" si="16"/>
-        <v>4.4861111111111107</v>
+        <v>4.405555555555555</v>
       </c>
       <c r="R53" s="32">
         <f t="shared" ca="1" si="16"/>
-        <v>5.4861111111111107</v>
+        <v>5.405555555555555</v>
       </c>
       <c r="S53" s="32">
         <f t="shared" ca="1" si="16"/>
-        <v>6.4861111111111107</v>
+        <v>6.405555555555555</v>
       </c>
       <c r="T53" s="32">
         <f t="shared" ca="1" si="16"/>
-        <v>7.4861111111111107</v>
+        <v>7.405555555555555</v>
       </c>
       <c r="U53" s="32">
         <f t="shared" ca="1" si="16"/>
-        <v>8.4861111111111107</v>
+        <v>8.405555555555555</v>
       </c>
       <c r="V53" s="32">
         <f t="shared" ca="1" si="16"/>
-        <v>9.4861111111111107</v>
+        <v>9.405555555555555</v>
       </c>
       <c r="W53" s="20"/>
       <c r="X53" s="20"/>
@@ -25636,7 +25774,7 @@
       <c r="U54" s="20"/>
       <c r="V54" s="24">
         <f ca="1">SUM(M52:V52)</f>
-        <v>7279.6444910151595</v>
+        <v>6684.845842763144</v>
       </c>
       <c r="W54" s="20"/>
       <c r="X54" s="20"/>
@@ -25674,7 +25812,7 @@
       <c r="U55" s="20"/>
       <c r="V55" s="24">
         <f ca="1">+(V40*(1+E19))*(1-(E19/E20))/(E18-E19)</f>
-        <v>29967.084187985009</v>
+        <v>26157.405332692302</v>
       </c>
       <c r="W55" s="20"/>
       <c r="X55" s="27" t="s">
@@ -25714,7 +25852,7 @@
       <c r="U56" s="71"/>
       <c r="V56" s="72">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>14440.526559317432</v>
+        <v>12683.107489327333</v>
       </c>
       <c r="W56" s="20"/>
       <c r="X56" s="20"/>
@@ -25752,7 +25890,7 @@
       <c r="U57" s="74"/>
       <c r="V57" s="75">
         <f ca="1">V54+V56</f>
-        <v>21720.171050332592</v>
+        <v>19367.953332090477</v>
       </c>
       <c r="W57" s="20"/>
       <c r="X57" s="20"/>
@@ -25790,7 +25928,7 @@
       <c r="U58" s="20"/>
       <c r="V58" s="76">
         <f>+Main!I5</f>
-        <v>1514.729</v>
+        <v>189.73699999999999</v>
       </c>
       <c r="W58" s="20"/>
       <c r="X58" s="20"/>
@@ -25866,7 +26004,7 @@
       <c r="U60" s="20"/>
       <c r="V60" s="76">
         <f ca="1">V57+V58-V59</f>
-        <v>23234.900050332591</v>
+        <v>19557.690332090478</v>
       </c>
       <c r="W60" s="20"/>
       <c r="X60" s="20"/>
@@ -25904,7 +26042,7 @@
       <c r="U61" s="71"/>
       <c r="V61" s="77">
         <f>+Main!I3</f>
-        <v>108.437957</v>
+        <v>105.594064</v>
       </c>
       <c r="W61" s="20"/>
       <c r="X61" s="20"/>
@@ -25942,7 +26080,7 @@
       <c r="U62" s="20"/>
       <c r="V62" s="76">
         <f ca="1">V60/V61</f>
-        <v>214.26906862817964</v>
+        <v>185.21581224575729</v>
       </c>
       <c r="W62" s="20"/>
       <c r="X62" s="20"/>
@@ -26167,7 +26305,7 @@
       </c>
       <c r="C69" s="79">
         <f ca="1">+J4</f>
-        <v>214.26906862817964</v>
+        <v>185.21581224575729</v>
       </c>
       <c r="D69" s="80"/>
       <c r="E69" s="80"/>
@@ -26183,7 +26321,7 @@
       </c>
       <c r="N69" s="79">
         <f ca="1">+J4</f>
-        <v>214.26906862817964</v>
+        <v>185.21581224575729</v>
       </c>
       <c r="O69" s="80"/>
       <c r="P69" s="80"/>
